--- a/data/input/订单汇总.xlsx
+++ b/data/input/订单汇总.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,16 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>套餐明细</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>赠品信息</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
@@ -521,22 +531,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -545,20 +555,20 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12800</v>
+        <v>2800</v>
       </c>
       <c r="J2" t="n">
         <v>0.9</v>
       </c>
       <c r="K2" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -575,6 +585,8 @@
         <v>0</v>
       </c>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -594,44 +606,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CU001</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>张小美</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>手术</t>
+          <t>疗程</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8800</v>
+        <v>5800</v>
       </c>
       <c r="J3" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="K3" t="n">
-        <v>7480</v>
+        <v>4350</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -648,6 +660,8 @@
         <v>0</v>
       </c>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -667,22 +681,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>瘦脸针</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,36 +705,38 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>980</v>
+        <v>2800</v>
       </c>
       <c r="J4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K4" t="n">
-        <v>833</v>
+        <v>2520</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -740,22 +756,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>玻尿酸填充</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -764,20 +780,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>980</v>
+        <v>3800</v>
       </c>
       <c r="J5" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>833</v>
+        <v>3040</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -794,6 +810,8 @@
         <v>0</v>
       </c>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -813,22 +831,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CU008</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>郑思思</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>玻尿酸填充</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -837,36 +855,38 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3800</v>
+        <v>12800</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3040</v>
+        <v>11520</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -886,22 +906,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>孙倩倩</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>玻尿酸填充</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,20 +930,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>12800</v>
+        <v>3800</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>11520</v>
+        <v>3040</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -940,6 +960,8 @@
         <v>0</v>
       </c>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -959,60 +981,74 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CU008</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>郑思思</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>玻尿酸填充</t>
+          <t>抗衰紧致套餐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>单次</t>
+          <t>套餐</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3800</v>
+        <v>25800</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="K8" t="n">
-        <v>3040</v>
+        <v>20124</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>[{"name": "热玛吉", "price": 12800, "quantity": 1}, {"name": "水光针", "price": 980, "quantity": 3}, {"name": "光子嫩肤", "price": 1500, "quantity": 3}]</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>[{"name": "修复面膜", "price": 380, "quantity": 1}, {"name": "精华液", "price": 580, "quantity": 1}]</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>含3项内容+2个赠品</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1032,44 +1068,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU004</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>赵丽丽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>面部焕新套餐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>疗程</t>
+          <t>套餐</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5800</v>
+        <v>12800</v>
       </c>
       <c r="J9" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="K9" t="n">
-        <v>4350</v>
+        <v>10496</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1083,9 +1119,23 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>[{"name": "玻尿酸填充", "price": 3800, "quantity": 2}, {"name": "瘦脸针", "price": 2800, "quantity": 1}]</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>[{"name": "导入护理", "price": 680, "quantity": 1}]</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>含2项内容+1个赠品</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1115,34 +1165,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>I006</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>瘦脸针</t>
+          <t>光子嫩肤疗程</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>单次</t>
+          <t>疗程</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2800</v>
+        <v>5800</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="K10" t="n">
-        <v>2520</v>
+        <v>4350</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1159,6 +1209,8 @@
         <v>0</v>
       </c>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1178,60 +1230,62 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU007</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>吴莹莹</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>水光针</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>手术</t>
+          <t>单次</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>8800</v>
+        <v>980</v>
       </c>
       <c r="J11" t="n">
         <v>0.85</v>
       </c>
       <c r="K11" t="n">
-        <v>7480</v>
+        <v>833</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1251,12 +1305,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1288,23 +1342,25 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1334,12 +1390,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>I006</t>
+          <t>I003</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>瘦脸针</t>
+          <t>玻尿酸填充</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1348,20 +1404,20 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2800</v>
+        <v>3800</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2520</v>
+        <v>3040</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1378,6 +1434,8 @@
         <v>0</v>
       </c>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1397,60 +1455,62 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU005</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>孙倩倩</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>双眼皮手术</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>单次</t>
+          <t>手术</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>980</v>
+        <v>8800</v>
       </c>
       <c r="J14" t="n">
         <v>0.85</v>
       </c>
       <c r="K14" t="n">
-        <v>833</v>
+        <v>7480</v>
       </c>
       <c r="L14" t="n">
         <v>5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1470,12 +1530,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CU005</t>
+          <t>CU008</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>孙倩倩</t>
+          <t>郑思思</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1503,27 +1563,29 @@
         <v>2520</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1533,32 +1595,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海浦东店</t>
+          <t>广州天河店</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CU003</t>
+          <t>CU008</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>王芳芳</t>
+          <t>郑思思</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1567,36 +1629,38 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>980</v>
+        <v>12800</v>
       </c>
       <c r="J16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>833</v>
+        <v>11520</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1606,12 +1670,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海浦东店</t>
+          <t>广州天河店</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1626,50 +1690,52 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>疗程</t>
+          <t>单次</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5800</v>
+        <v>12800</v>
       </c>
       <c r="J17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4350</v>
+        <v>11520</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1689,22 +1755,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CU007</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>吴莹莹</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>I003</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>玻尿酸填充</t>
+          <t>水光针</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1713,36 +1779,38 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3800</v>
+        <v>980</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="K18" t="n">
-        <v>3040</v>
+        <v>833</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1762,60 +1830,62 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU006</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>周晶晶</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>水光针</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>手术</t>
+          <t>单次</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8800</v>
+        <v>980</v>
       </c>
       <c r="J19" t="n">
         <v>0.85</v>
       </c>
       <c r="K19" t="n">
-        <v>7480</v>
+        <v>833</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1835,60 +1905,62 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>光子嫩肤</t>
+          <t>水光针</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>疗程</t>
+          <t>单次</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5800</v>
+        <v>980</v>
       </c>
       <c r="J20" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="K20" t="n">
-        <v>4350</v>
+        <v>833</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1908,44 +1980,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CU008</t>
+          <t>CU001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>郑思思</t>
+          <t>张小美</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>I005</t>
+          <t>I002</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>双眼皮手术</t>
+          <t>热玛吉</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>手术</t>
+          <t>单次</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>8800</v>
+        <v>12800</v>
       </c>
       <c r="J21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="n">
-        <v>7480</v>
+        <v>11520</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1962,6 +2034,8 @@
         <v>0</v>
       </c>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1981,22 +2055,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CU005</t>
+          <t>CU008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>孙倩倩</t>
+          <t>郑思思</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I006</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>瘦脸针（上月订单）</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2005,36 +2079,42 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>12800</v>
+        <v>2800</v>
       </c>
       <c r="J22" t="n">
         <v>0.9</v>
       </c>
       <c r="K22" t="n">
-        <v>11520</v>
+        <v>2520</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>陈咨询师</t>
+          <t>刘咨询师</t>
         </is>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>跨月测试数据</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2044,70 +2124,76 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CU004</t>
+          <t>CU007</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>赵丽丽</t>
+          <t>吴莹莹</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>I002</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>热玛吉</t>
+          <t>光子嫩肤疗程（上月订单）</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>单次</t>
+          <t>疗程</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>12800</v>
+        <v>5800</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="K23" t="n">
-        <v>11520</v>
+        <v>4350</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>周咨询师</t>
+          <t>陈咨询师</t>
         </is>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>跨月测试数据</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2117,143 +2203,76 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>广州天河店</t>
+          <t>北京朝阳店</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CU006</t>
+          <t>CU003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>周晶晶</t>
+          <t>王芳芳</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>I005</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>水光针</t>
+          <t>双眼皮手术（上月订单）</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>单次</t>
+          <t>手术</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>980</v>
+        <v>8800</v>
       </c>
       <c r="J24" t="n">
         <v>0.85</v>
       </c>
       <c r="K24" t="n">
-        <v>833</v>
+        <v>7480</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>刘咨询师</t>
+          <t>周咨询师</t>
         </is>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ORD000024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>广州天河店</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CU004</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>赵丽丽</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>I005</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>双眼皮手术</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>手术</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>8800</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7480</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>陈咨询师</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>跨月测试数据</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
